--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N95_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.17275934640607</v>
+        <v>3.440573393790987</v>
       </c>
       <c r="D2" t="n">
-        <v>14.69066627324472</v>
+        <v>2.387233269402268</v>
       </c>
       <c r="E2" t="n">
-        <v>7.636629330172981</v>
+        <v>1.240952266153109</v>
       </c>
       <c r="F2" t="n">
-        <v>7.617996716894454</v>
+        <v>1.237924466495349</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.64034565224091</v>
+        <v>3.841556168489149</v>
       </c>
       <c r="D3" t="n">
-        <v>23.86599548323583</v>
+        <v>3.878224266025822</v>
       </c>
       <c r="E3" t="n">
-        <v>7.636629330172981</v>
+        <v>1.240952266153109</v>
       </c>
       <c r="F3" t="n">
-        <v>7.617996716894454</v>
+        <v>1.237924466495349</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.63555079993433</v>
+        <v>3.678277004989329</v>
       </c>
       <c r="D4" t="n">
-        <v>22.81033618471691</v>
+        <v>3.706679630016497</v>
       </c>
       <c r="E4" t="n">
-        <v>7.636629330172981</v>
+        <v>1.240952266153109</v>
       </c>
       <c r="F4" t="n">
-        <v>7.617996716894454</v>
+        <v>1.237924466495349</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.963639511132565</v>
+        <v>0.8065914205590419</v>
       </c>
       <c r="D5" t="n">
-        <v>4.88965792001544</v>
+        <v>0.7945694120025091</v>
       </c>
       <c r="E5" t="n">
-        <v>7.636629330172981</v>
+        <v>1.240952266153109</v>
       </c>
       <c r="F5" t="n">
-        <v>7.617996716894454</v>
+        <v>1.237924466495349</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
